--- a/Excel/Conditional formatting.xlsx
+++ b/Excel/Conditional formatting.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cd31b31aebe99429/Desktop/Project2/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7565326F-ACD7-4961-8747-B10355D50635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{7565326F-ACD7-4961-8747-B10355D50635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60F40700-8F7B-4BC3-9A99-0BD35CCD91C5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{386A7A78-081E-47F2-AEF1-61B993D563D0}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="32">
   <si>
     <t>first_name</t>
   </si>
@@ -145,6 +145,9 @@
   <si>
     <t>X-Ray</t>
   </si>
+  <si>
+    <t>Average</t>
+  </si>
 </sst>
 </file>
 
@@ -179,9 +182,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -566,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E299518-EF8E-4AD1-9E04-A59AD846C469}">
-  <dimension ref="A1:F201"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -577,7 +579,7 @@
     <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -596,18 +598,21 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="H1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
         <v>4279.38</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
       <c r="E2">
@@ -616,18 +621,22 @@
       <c r="F2">
         <v>1649.67</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="H2">
+        <f>AVERAGE(C:C)</f>
+        <v>2756.2492499999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
       <c r="C3">
         <v>3627.28</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3">
@@ -637,17 +646,17 @@
         <v>997.57</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4">
         <v>771.2</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4">
@@ -657,17 +666,17 @@
         <v>-1858.51</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5">
         <v>1565.92</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>8</v>
       </c>
       <c r="E5">
@@ -677,17 +686,17 @@
         <v>-1063.79</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6">
         <v>3512.69</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6">
@@ -697,17 +706,17 @@
         <v>882.98</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>17</v>
       </c>
       <c r="C7">
         <v>2835.77</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>8</v>
       </c>
       <c r="E7">
@@ -717,17 +726,17 @@
         <v>206.06</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8">
         <v>857.39</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>8</v>
       </c>
       <c r="E8">
@@ -737,17 +746,17 @@
         <v>-1772.32</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>7</v>
       </c>
       <c r="C9">
         <v>2426.9</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>8</v>
       </c>
       <c r="E9">
@@ -757,17 +766,17 @@
         <v>-202.81</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>19</v>
       </c>
       <c r="C10">
         <v>4945.03</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>8</v>
       </c>
       <c r="E10">
@@ -777,17 +786,17 @@
         <v>2315.3200000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>17</v>
       </c>
       <c r="C11">
         <v>1871.06</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>8</v>
       </c>
       <c r="E11">
@@ -797,17 +806,17 @@
         <v>-758.65</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>14</v>
       </c>
       <c r="C12">
         <v>2735.45</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>8</v>
       </c>
       <c r="E12">
@@ -817,17 +826,17 @@
         <v>105.74</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>20</v>
       </c>
       <c r="C13">
         <v>2259.08</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>8</v>
       </c>
       <c r="E13">
@@ -837,17 +846,17 @@
         <v>-370.63</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>14</v>
       </c>
       <c r="C14">
         <v>930.72</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s">
         <v>8</v>
       </c>
       <c r="E14">
@@ -857,17 +866,17 @@
         <v>-1698.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>7</v>
       </c>
       <c r="C15">
         <v>2477.8000000000002</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" t="s">
         <v>8</v>
       </c>
       <c r="E15">
@@ -877,17 +886,17 @@
         <v>-151.91</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>12</v>
       </c>
       <c r="C16">
         <v>2212.8000000000002</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" t="s">
         <v>8</v>
       </c>
       <c r="E16">
@@ -898,16 +907,16 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>7</v>
       </c>
       <c r="C17">
         <v>4178.5200000000004</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" t="s">
         <v>8</v>
       </c>
       <c r="E17">
@@ -918,16 +927,16 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>17</v>
       </c>
       <c r="C18">
         <v>1023.65</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" t="s">
         <v>8</v>
       </c>
       <c r="E18">
@@ -938,16 +947,16 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>12</v>
       </c>
       <c r="C19">
         <v>4834.0200000000004</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" t="s">
         <v>8</v>
       </c>
       <c r="E19">
@@ -958,16 +967,16 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>19</v>
       </c>
       <c r="C20">
         <v>4687.68</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" t="s">
         <v>8</v>
       </c>
       <c r="E20">
@@ -978,16 +987,16 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>19</v>
       </c>
       <c r="C21">
         <v>4113.62</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" t="s">
         <v>8</v>
       </c>
       <c r="E21">
@@ -998,16 +1007,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" t="s">
         <v>24</v>
       </c>
       <c r="C22">
         <v>1438.3</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" t="s">
         <v>8</v>
       </c>
       <c r="E22">
@@ -1018,16 +1027,16 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" t="s">
         <v>17</v>
       </c>
       <c r="C23">
         <v>4964.71</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" t="s">
         <v>8</v>
       </c>
       <c r="E23">
@@ -1038,16 +1047,16 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" t="s">
         <v>19</v>
       </c>
       <c r="C24">
         <v>2512.41</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" t="s">
         <v>8</v>
       </c>
       <c r="E24">
@@ -1058,16 +1067,16 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" t="s">
         <v>10</v>
       </c>
       <c r="C25">
         <v>1472.17</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" t="s">
         <v>8</v>
       </c>
       <c r="E25">
@@ -1078,16 +1087,16 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" t="s">
         <v>7</v>
       </c>
       <c r="C26">
         <v>1381</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" t="s">
         <v>8</v>
       </c>
       <c r="E26">
@@ -1098,16 +1107,16 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" t="s">
         <v>19</v>
       </c>
       <c r="C27">
         <v>2360.9699999999998</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" t="s">
         <v>8</v>
       </c>
       <c r="E27">
@@ -1118,16 +1127,16 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" t="s">
         <v>16</v>
       </c>
       <c r="C28">
         <v>1684.01</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" t="s">
         <v>8</v>
       </c>
       <c r="E28">
@@ -1138,16 +1147,16 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" t="s">
         <v>16</v>
       </c>
       <c r="C29">
         <v>1315.17</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" t="s">
         <v>8</v>
       </c>
       <c r="E29">
@@ -1158,16 +1167,16 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>15</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" t="s">
         <v>24</v>
       </c>
       <c r="C30">
         <v>901.06</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" t="s">
         <v>8</v>
       </c>
       <c r="E30">
@@ -1178,16 +1187,16 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" t="s">
         <v>19</v>
       </c>
       <c r="C31">
         <v>1316.47</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" t="s">
         <v>8</v>
       </c>
       <c r="E31">
@@ -1198,16 +1207,16 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" t="s">
         <v>20</v>
       </c>
       <c r="C32">
         <v>534.03</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" t="s">
         <v>8</v>
       </c>
       <c r="E32">
@@ -1218,16 +1227,16 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>9</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" t="s">
         <v>12</v>
       </c>
       <c r="C33">
         <v>616.15</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" t="s">
         <v>8</v>
       </c>
       <c r="E33">
@@ -1238,16 +1247,16 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" t="s">
         <v>26</v>
       </c>
       <c r="C34">
         <v>4671.5</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" t="s">
         <v>8</v>
       </c>
       <c r="E34">
@@ -1258,16 +1267,16 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>23</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" t="s">
         <v>12</v>
       </c>
       <c r="C35">
         <v>3941.97</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" t="s">
         <v>8</v>
       </c>
       <c r="E35">
@@ -1278,16 +1287,16 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" t="s">
         <v>24</v>
       </c>
       <c r="C36">
         <v>3492.1</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" t="s">
         <v>8</v>
       </c>
       <c r="E36">
@@ -1298,16 +1307,16 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>11</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" t="s">
         <v>26</v>
       </c>
       <c r="C37">
         <v>2064.0700000000002</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" t="s">
         <v>8</v>
       </c>
       <c r="E37">
@@ -1318,16 +1327,16 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" t="s">
         <v>26</v>
       </c>
       <c r="C38">
         <v>2675.96</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" t="s">
         <v>8</v>
       </c>
       <c r="E38">
@@ -1338,16 +1347,16 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>6</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" t="s">
         <v>24</v>
       </c>
       <c r="C39">
         <v>2911.22</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" t="s">
         <v>8</v>
       </c>
       <c r="E39">
@@ -1358,16 +1367,16 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>15</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" t="s">
         <v>17</v>
       </c>
       <c r="C40">
         <v>3030.34</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" t="s">
         <v>8</v>
       </c>
       <c r="E40">
@@ -1378,16 +1387,16 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>22</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" t="s">
         <v>19</v>
       </c>
       <c r="C41">
         <v>695.36</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" t="s">
         <v>8</v>
       </c>
       <c r="E41">
@@ -1398,16 +1407,16 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>22</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" t="s">
         <v>17</v>
       </c>
       <c r="C42">
         <v>770.64</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" t="s">
         <v>8</v>
       </c>
       <c r="E42">
@@ -1418,16 +1427,16 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>22</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" t="s">
         <v>17</v>
       </c>
       <c r="C43">
         <v>4781.32</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" t="s">
         <v>8</v>
       </c>
       <c r="E43">
@@ -1438,16 +1447,16 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>11</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" t="s">
         <v>26</v>
       </c>
       <c r="C44">
         <v>3010.03</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" t="s">
         <v>8</v>
       </c>
       <c r="E44">
@@ -1458,16 +1467,16 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>11</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" t="s">
         <v>17</v>
       </c>
       <c r="C45">
         <v>3478.28</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" t="s">
         <v>8</v>
       </c>
       <c r="E45">
@@ -1478,16 +1487,16 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>22</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" t="s">
         <v>19</v>
       </c>
       <c r="C46">
         <v>4478.93</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" t="s">
         <v>8</v>
       </c>
       <c r="E46">
@@ -1498,16 +1507,16 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>23</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" t="s">
         <v>24</v>
       </c>
       <c r="C47">
         <v>3228.14</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" t="s">
         <v>8</v>
       </c>
       <c r="E47">
@@ -1518,16 +1527,16 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>15</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" t="s">
         <v>16</v>
       </c>
       <c r="C48">
         <v>3384.37</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" t="s">
         <v>8</v>
       </c>
       <c r="E48">
@@ -1538,16 +1547,16 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>11</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" t="s">
         <v>20</v>
       </c>
       <c r="C49">
         <v>3249.41</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" t="s">
         <v>8</v>
       </c>
       <c r="E49">
@@ -1558,16 +1567,16 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>11</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" t="s">
         <v>17</v>
       </c>
       <c r="C50">
         <v>2349.63</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" t="s">
         <v>8</v>
       </c>
       <c r="E50">
@@ -1578,16 +1587,16 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>18</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" t="s">
         <v>17</v>
       </c>
       <c r="C51">
         <v>4672.3</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" t="s">
         <v>27</v>
       </c>
       <c r="E51">
@@ -1598,16 +1607,16 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>9</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" t="s">
         <v>20</v>
       </c>
       <c r="C52">
         <v>582.04999999999995</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" t="s">
         <v>27</v>
       </c>
       <c r="E52">
@@ -1618,16 +1627,16 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>15</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" t="s">
         <v>16</v>
       </c>
       <c r="C53">
         <v>2082.3000000000002</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" t="s">
         <v>27</v>
       </c>
       <c r="E53">
@@ -1638,16 +1647,16 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="1" t="s">
+      <c r="A54" t="s">
         <v>25</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" t="s">
         <v>14</v>
       </c>
       <c r="C54">
         <v>1781.93</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" t="s">
         <v>27</v>
       </c>
       <c r="E54">
@@ -1658,16 +1667,16 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="1" t="s">
+      <c r="A55" t="s">
         <v>11</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" t="s">
         <v>26</v>
       </c>
       <c r="C55">
         <v>3722.68</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D55" t="s">
         <v>27</v>
       </c>
       <c r="E55">
@@ -1678,16 +1687,16 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="1" t="s">
+      <c r="A56" t="s">
         <v>9</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" t="s">
         <v>26</v>
       </c>
       <c r="C56">
         <v>1726.81</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D56" t="s">
         <v>27</v>
       </c>
       <c r="E56">
@@ -1698,16 +1707,16 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="1" t="s">
+      <c r="A57" t="s">
         <v>25</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" t="s">
         <v>19</v>
       </c>
       <c r="C57">
         <v>2863.24</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D57" t="s">
         <v>27</v>
       </c>
       <c r="E57">
@@ -1718,16 +1727,16 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="1" t="s">
+      <c r="A58" t="s">
         <v>9</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" t="s">
         <v>7</v>
       </c>
       <c r="C58">
         <v>3690.71</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D58" t="s">
         <v>27</v>
       </c>
       <c r="E58">
@@ -1738,16 +1747,16 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="1" t="s">
+      <c r="A59" t="s">
         <v>13</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" t="s">
         <v>7</v>
       </c>
       <c r="C59">
         <v>1526.36</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D59" t="s">
         <v>27</v>
       </c>
       <c r="E59">
@@ -1758,16 +1767,16 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="1" t="s">
+      <c r="A60" t="s">
         <v>23</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" t="s">
         <v>26</v>
       </c>
       <c r="C60">
         <v>1454.2</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" t="s">
         <v>27</v>
       </c>
       <c r="E60">
@@ -1778,16 +1787,16 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="1" t="s">
+      <c r="A61" t="s">
         <v>22</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" t="s">
         <v>24</v>
       </c>
       <c r="C61">
         <v>4550.1000000000004</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D61" t="s">
         <v>27</v>
       </c>
       <c r="E61">
@@ -1798,16 +1807,16 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="1" t="s">
+      <c r="A62" t="s">
         <v>22</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" t="s">
         <v>19</v>
       </c>
       <c r="C62">
         <v>2090.4</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" t="s">
         <v>27</v>
       </c>
       <c r="E62">
@@ -1818,16 +1827,16 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="1" t="s">
+      <c r="A63" t="s">
         <v>6</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" t="s">
         <v>26</v>
       </c>
       <c r="C63">
         <v>929.91</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" t="s">
         <v>27</v>
       </c>
       <c r="E63">
@@ -1838,16 +1847,16 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="1" t="s">
+      <c r="A64" t="s">
         <v>22</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" t="s">
         <v>17</v>
       </c>
       <c r="C64">
         <v>4382.59</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" t="s">
         <v>27</v>
       </c>
       <c r="E64">
@@ -1858,16 +1867,16 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="1" t="s">
+      <c r="A65" t="s">
         <v>22</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" t="s">
         <v>17</v>
       </c>
       <c r="C65">
         <v>1475.33</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D65" t="s">
         <v>27</v>
       </c>
       <c r="E65">
@@ -1878,16 +1887,16 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="1" t="s">
+      <c r="A66" t="s">
         <v>18</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" t="s">
         <v>20</v>
       </c>
       <c r="C66">
         <v>606.37</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D66" t="s">
         <v>27</v>
       </c>
       <c r="E66">
@@ -1898,16 +1907,16 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="1" t="s">
+      <c r="A67" t="s">
         <v>11</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" t="s">
         <v>20</v>
       </c>
       <c r="C67">
         <v>2960.14</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" t="s">
         <v>27</v>
       </c>
       <c r="E67">
@@ -1918,16 +1927,16 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
+      <c r="A68" t="s">
         <v>22</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" t="s">
         <v>17</v>
       </c>
       <c r="C68">
         <v>1543.76</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D68" t="s">
         <v>27</v>
       </c>
       <c r="E68">
@@ -1938,16 +1947,16 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="1" t="s">
+      <c r="A69" t="s">
         <v>22</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" t="s">
         <v>19</v>
       </c>
       <c r="C69">
         <v>3175.14</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D69" t="s">
         <v>27</v>
       </c>
       <c r="E69">
@@ -1958,16 +1967,16 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="1" t="s">
+      <c r="A70" t="s">
         <v>11</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" t="s">
         <v>12</v>
       </c>
       <c r="C70">
         <v>1113.98</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D70" t="s">
         <v>27</v>
       </c>
       <c r="E70">
@@ -1978,16 +1987,16 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="1" t="s">
+      <c r="A71" t="s">
         <v>22</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" t="s">
         <v>19</v>
       </c>
       <c r="C71">
         <v>3729.19</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="D71" t="s">
         <v>27</v>
       </c>
       <c r="E71">
@@ -1998,16 +2007,16 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="1" t="s">
+      <c r="A72" t="s">
         <v>15</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" t="s">
         <v>17</v>
       </c>
       <c r="C72">
         <v>4960.6499999999996</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D72" t="s">
         <v>27</v>
       </c>
       <c r="E72">
@@ -2018,16 +2027,16 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="1" t="s">
+      <c r="A73" t="s">
         <v>11</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" t="s">
         <v>17</v>
       </c>
       <c r="C73">
         <v>1077.77</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="D73" t="s">
         <v>27</v>
       </c>
       <c r="E73">
@@ -2038,16 +2047,16 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="1" t="s">
+      <c r="A74" t="s">
         <v>6</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" t="s">
         <v>24</v>
       </c>
       <c r="C74">
         <v>968.49</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D74" t="s">
         <v>27</v>
       </c>
       <c r="E74">
@@ -2058,16 +2067,16 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="1" t="s">
+      <c r="A75" t="s">
         <v>25</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" t="s">
         <v>19</v>
       </c>
       <c r="C75">
         <v>3102.74</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="D75" t="s">
         <v>27</v>
       </c>
       <c r="E75">
@@ -2078,16 +2087,16 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="1" t="s">
+      <c r="A76" t="s">
         <v>6</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" t="s">
         <v>7</v>
       </c>
       <c r="C76">
         <v>804.26</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D76" t="s">
         <v>27</v>
       </c>
       <c r="E76">
@@ -2098,16 +2107,16 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="1" t="s">
+      <c r="A77" t="s">
         <v>22</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" t="s">
         <v>17</v>
       </c>
       <c r="C77">
         <v>3428.95</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D77" t="s">
         <v>27</v>
       </c>
       <c r="E77">
@@ -2118,16 +2127,16 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="1" t="s">
+      <c r="A78" t="s">
         <v>22</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" t="s">
         <v>17</v>
       </c>
       <c r="C78">
         <v>2898.31</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="D78" t="s">
         <v>27</v>
       </c>
       <c r="E78">
@@ -2138,16 +2147,16 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="1" t="s">
+      <c r="A79" t="s">
         <v>22</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" t="s">
         <v>19</v>
       </c>
       <c r="C79">
         <v>1959.5</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="D79" t="s">
         <v>27</v>
       </c>
       <c r="E79">
@@ -2158,16 +2167,16 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="1" t="s">
+      <c r="A80" t="s">
         <v>13</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" t="s">
         <v>14</v>
       </c>
       <c r="C80">
         <v>1404.2</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D80" t="s">
         <v>27</v>
       </c>
       <c r="E80">
@@ -2178,16 +2187,16 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="1" t="s">
+      <c r="A81" t="s">
         <v>18</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" t="s">
         <v>20</v>
       </c>
       <c r="C81">
         <v>3689.35</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="D81" t="s">
         <v>27</v>
       </c>
       <c r="E81">
@@ -2198,16 +2207,16 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="1" t="s">
+      <c r="A82" t="s">
         <v>21</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" t="s">
         <v>26</v>
       </c>
       <c r="C82">
         <v>2286.42</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="D82" t="s">
         <v>27</v>
       </c>
       <c r="E82">
@@ -2218,16 +2227,16 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="1" t="s">
+      <c r="A83" t="s">
         <v>11</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" t="s">
         <v>17</v>
       </c>
       <c r="C83">
         <v>3202.67</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="D83" t="s">
         <v>27</v>
       </c>
       <c r="E83">
@@ -2238,16 +2247,16 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="1" t="s">
+      <c r="A84" t="s">
         <v>23</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" t="s">
         <v>19</v>
       </c>
       <c r="C84">
         <v>4406.26</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="D84" t="s">
         <v>27</v>
       </c>
       <c r="E84">
@@ -2258,16 +2267,16 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="1" t="s">
+      <c r="A85" t="s">
         <v>11</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" t="s">
         <v>17</v>
       </c>
       <c r="C85">
         <v>4055.14</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="D85" t="s">
         <v>27</v>
       </c>
       <c r="E85">
@@ -2278,16 +2287,16 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="1" t="s">
+      <c r="A86" t="s">
         <v>15</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" t="s">
         <v>16</v>
       </c>
       <c r="C86">
         <v>1158.68</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D86" t="s">
         <v>27</v>
       </c>
       <c r="E86">
@@ -2298,16 +2307,16 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="1" t="s">
+      <c r="A87" t="s">
         <v>9</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" t="s">
         <v>7</v>
       </c>
       <c r="C87">
         <v>2777.64</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="D87" t="s">
         <v>27</v>
       </c>
       <c r="E87">
@@ -2318,16 +2327,16 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="1" t="s">
+      <c r="A88" t="s">
         <v>25</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B88" t="s">
         <v>14</v>
       </c>
       <c r="C88">
         <v>3383.72</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="D88" t="s">
         <v>27</v>
       </c>
       <c r="E88">
@@ -2338,16 +2347,16 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="1" t="s">
+      <c r="A89" t="s">
         <v>15</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B89" t="s">
         <v>10</v>
       </c>
       <c r="C89">
         <v>4704.96</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="D89" t="s">
         <v>28</v>
       </c>
       <c r="E89">
@@ -2358,16 +2367,16 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="1" t="s">
+      <c r="A90" t="s">
         <v>18</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" t="s">
         <v>20</v>
       </c>
       <c r="C90">
         <v>2296.92</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="D90" t="s">
         <v>28</v>
       </c>
       <c r="E90">
@@ -2378,16 +2387,16 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="1" t="s">
+      <c r="A91" t="s">
         <v>15</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" t="s">
         <v>17</v>
       </c>
       <c r="C91">
         <v>2153.9</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="D91" t="s">
         <v>28</v>
       </c>
       <c r="E91">
@@ -2398,16 +2407,16 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="1" t="s">
+      <c r="A92" t="s">
         <v>22</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" t="s">
         <v>19</v>
       </c>
       <c r="C92">
         <v>1096.3599999999999</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="D92" t="s">
         <v>28</v>
       </c>
       <c r="E92">
@@ -2418,16 +2427,16 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="1" t="s">
+      <c r="A93" t="s">
         <v>18</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" t="s">
         <v>19</v>
       </c>
       <c r="C93">
         <v>4379.07</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="D93" t="s">
         <v>28</v>
       </c>
       <c r="E93">
@@ -2438,16 +2447,16 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="1" t="s">
+      <c r="A94" t="s">
         <v>18</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B94" t="s">
         <v>20</v>
       </c>
       <c r="C94">
         <v>2526.67</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="D94" t="s">
         <v>28</v>
       </c>
       <c r="E94">
@@ -2458,16 +2467,16 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="1" t="s">
+      <c r="A95" t="s">
         <v>21</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B95" t="s">
         <v>10</v>
       </c>
       <c r="C95">
         <v>4966.18</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="D95" t="s">
         <v>28</v>
       </c>
       <c r="E95">
@@ -2478,16 +2487,16 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="1" t="s">
+      <c r="A96" t="s">
         <v>18</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B96" t="s">
         <v>17</v>
       </c>
       <c r="C96">
         <v>4460.3599999999997</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="D96" t="s">
         <v>28</v>
       </c>
       <c r="E96">
@@ -2498,16 +2507,16 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="1" t="s">
+      <c r="A97" t="s">
         <v>15</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B97" t="s">
         <v>16</v>
       </c>
       <c r="C97">
         <v>3388.87</v>
       </c>
-      <c r="D97" s="1" t="s">
+      <c r="D97" t="s">
         <v>28</v>
       </c>
       <c r="E97">
@@ -2518,16 +2527,16 @@
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="1" t="s">
+      <c r="A98" t="s">
         <v>15</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B98" t="s">
         <v>10</v>
       </c>
       <c r="C98">
         <v>3231.92</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="D98" t="s">
         <v>28</v>
       </c>
       <c r="E98">
@@ -2538,16 +2547,16 @@
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="1" t="s">
+      <c r="A99" t="s">
         <v>9</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B99" t="s">
         <v>7</v>
       </c>
       <c r="C99">
         <v>3731.55</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="D99" t="s">
         <v>28</v>
       </c>
       <c r="E99">
@@ -2558,16 +2567,16 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="1" t="s">
+      <c r="A100" t="s">
         <v>25</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B100" t="s">
         <v>14</v>
       </c>
       <c r="C100">
         <v>3306.14</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="D100" t="s">
         <v>28</v>
       </c>
       <c r="E100">
@@ -2578,16 +2587,16 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="1" t="s">
+      <c r="A101" t="s">
         <v>22</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B101" t="s">
         <v>19</v>
       </c>
       <c r="C101">
         <v>3565.03</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="D101" t="s">
         <v>28</v>
       </c>
       <c r="E101">
@@ -2598,16 +2607,16 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="1" t="s">
+      <c r="A102" t="s">
         <v>23</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B102" t="s">
         <v>26</v>
       </c>
       <c r="C102">
         <v>3605.02</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="D102" t="s">
         <v>28</v>
       </c>
       <c r="E102">
@@ -2618,16 +2627,16 @@
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="1" t="s">
+      <c r="A103" t="s">
         <v>18</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B103" t="s">
         <v>7</v>
       </c>
       <c r="C103">
         <v>4186.3500000000004</v>
       </c>
-      <c r="D103" s="1" t="s">
+      <c r="D103" t="s">
         <v>28</v>
       </c>
       <c r="E103">
@@ -2638,16 +2647,16 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="1" t="s">
+      <c r="A104" t="s">
         <v>22</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B104" t="s">
         <v>17</v>
       </c>
       <c r="C104">
         <v>4217.3</v>
       </c>
-      <c r="D104" s="1" t="s">
+      <c r="D104" t="s">
         <v>28</v>
       </c>
       <c r="E104">
@@ -2658,16 +2667,16 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="1" t="s">
+      <c r="A105" t="s">
         <v>9</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B105" t="s">
         <v>10</v>
       </c>
       <c r="C105">
         <v>4101.6000000000004</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="D105" t="s">
         <v>28</v>
       </c>
       <c r="E105">
@@ -2678,16 +2687,16 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="1" t="s">
+      <c r="A106" t="s">
         <v>22</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B106" t="s">
         <v>19</v>
       </c>
       <c r="C106">
         <v>3941.64</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="D106" t="s">
         <v>28</v>
       </c>
       <c r="E106">
@@ -2698,16 +2707,16 @@
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="1" t="s">
+      <c r="A107" t="s">
         <v>13</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B107" t="s">
         <v>7</v>
       </c>
       <c r="C107">
         <v>662.72</v>
       </c>
-      <c r="D107" s="1" t="s">
+      <c r="D107" t="s">
         <v>28</v>
       </c>
       <c r="E107">
@@ -2718,16 +2727,16 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="1" t="s">
+      <c r="A108" t="s">
         <v>15</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B108" t="s">
         <v>16</v>
       </c>
       <c r="C108">
         <v>1864.08</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="D108" t="s">
         <v>28</v>
       </c>
       <c r="E108">
@@ -2738,16 +2747,16 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="1" t="s">
+      <c r="A109" t="s">
         <v>22</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B109" t="s">
         <v>17</v>
       </c>
       <c r="C109">
         <v>2930.05</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="D109" t="s">
         <v>28</v>
       </c>
       <c r="E109">
@@ -2758,16 +2767,16 @@
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="1" t="s">
+      <c r="A110" t="s">
         <v>11</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B110" t="s">
         <v>17</v>
       </c>
       <c r="C110">
         <v>3787.93</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="D110" t="s">
         <v>28</v>
       </c>
       <c r="E110">
@@ -2778,16 +2787,16 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="1" t="s">
+      <c r="A111" t="s">
         <v>23</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="B111" t="s">
         <v>26</v>
       </c>
       <c r="C111">
         <v>894.39</v>
       </c>
-      <c r="D111" s="1" t="s">
+      <c r="D111" t="s">
         <v>28</v>
       </c>
       <c r="E111">
@@ -2798,16 +2807,16 @@
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="1" t="s">
+      <c r="A112" t="s">
         <v>23</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B112" t="s">
         <v>19</v>
       </c>
       <c r="C112">
         <v>4716.3100000000004</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="D112" t="s">
         <v>28</v>
       </c>
       <c r="E112">
@@ -2818,16 +2827,16 @@
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="1" t="s">
+      <c r="A113" t="s">
         <v>25</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B113" t="s">
         <v>14</v>
       </c>
       <c r="C113">
         <v>4671.66</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="D113" t="s">
         <v>28</v>
       </c>
       <c r="E113">
@@ -2838,16 +2847,16 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="1" t="s">
+      <c r="A114" t="s">
         <v>18</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B114" t="s">
         <v>7</v>
       </c>
       <c r="C114">
         <v>4126.66</v>
       </c>
-      <c r="D114" s="1" t="s">
+      <c r="D114" t="s">
         <v>28</v>
       </c>
       <c r="E114">
@@ -2858,16 +2867,16 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="1" t="s">
+      <c r="A115" t="s">
         <v>18</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B115" t="s">
         <v>20</v>
       </c>
       <c r="C115">
         <v>4126.97</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="D115" t="s">
         <v>28</v>
       </c>
       <c r="E115">
@@ -2878,16 +2887,16 @@
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="1" t="s">
+      <c r="A116" t="s">
         <v>21</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B116" t="s">
         <v>26</v>
       </c>
       <c r="C116">
         <v>3246.5</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="D116" t="s">
         <v>28</v>
       </c>
       <c r="E116">
@@ -2898,16 +2907,16 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="1" t="s">
+      <c r="A117" t="s">
         <v>23</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="B117" t="s">
         <v>26</v>
       </c>
       <c r="C117">
         <v>4158.4399999999996</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="D117" t="s">
         <v>28</v>
       </c>
       <c r="E117">
@@ -2918,16 +2927,16 @@
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="1" t="s">
+      <c r="A118" t="s">
         <v>22</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B118" t="s">
         <v>17</v>
       </c>
       <c r="C118">
         <v>1654.53</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="D118" t="s">
         <v>28</v>
       </c>
       <c r="E118">
@@ -2938,16 +2947,16 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="1" t="s">
+      <c r="A119" t="s">
         <v>9</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B119" t="s">
         <v>7</v>
       </c>
       <c r="C119">
         <v>2593.4299999999998</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="D119" t="s">
         <v>28</v>
       </c>
       <c r="E119">
@@ -2958,16 +2967,16 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="1" t="s">
+      <c r="A120" t="s">
         <v>22</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="B120" t="s">
         <v>19</v>
       </c>
       <c r="C120">
         <v>2686.42</v>
       </c>
-      <c r="D120" s="1" t="s">
+      <c r="D120" t="s">
         <v>28</v>
       </c>
       <c r="E120">
@@ -2978,16 +2987,16 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="1" t="s">
+      <c r="A121" t="s">
         <v>23</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B121" t="s">
         <v>26</v>
       </c>
       <c r="C121">
         <v>2406.8200000000002</v>
       </c>
-      <c r="D121" s="1" t="s">
+      <c r="D121" t="s">
         <v>28</v>
       </c>
       <c r="E121">
@@ -2998,16 +3007,16 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="1" t="s">
+      <c r="A122" t="s">
         <v>18</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B122" t="s">
         <v>17</v>
       </c>
       <c r="C122">
         <v>4799.8599999999997</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="D122" t="s">
         <v>28</v>
       </c>
       <c r="E122">
@@ -3018,16 +3027,16 @@
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="1" t="s">
+      <c r="A123" t="s">
         <v>15</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B123" t="s">
         <v>17</v>
       </c>
       <c r="C123">
         <v>1256.06</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="D123" t="s">
         <v>28</v>
       </c>
       <c r="E123">
@@ -3038,16 +3047,16 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="1" t="s">
+      <c r="A124" t="s">
         <v>18</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B124" t="s">
         <v>20</v>
       </c>
       <c r="C124">
         <v>1655.49</v>
       </c>
-      <c r="D124" s="1" t="s">
+      <c r="D124" t="s">
         <v>28</v>
       </c>
       <c r="E124">
@@ -3058,16 +3067,16 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="1" t="s">
+      <c r="A125" t="s">
         <v>6</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="B125" t="s">
         <v>24</v>
       </c>
       <c r="C125">
         <v>2976.02</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="D125" t="s">
         <v>29</v>
       </c>
       <c r="E125">
@@ -3078,16 +3087,16 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="1" t="s">
+      <c r="A126" t="s">
         <v>25</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B126" t="s">
         <v>19</v>
       </c>
       <c r="C126">
         <v>956.39</v>
       </c>
-      <c r="D126" s="1" t="s">
+      <c r="D126" t="s">
         <v>29</v>
       </c>
       <c r="E126">
@@ -3098,16 +3107,16 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="1" t="s">
+      <c r="A127" t="s">
         <v>11</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B127" t="s">
         <v>20</v>
       </c>
       <c r="C127">
         <v>975.49</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="D127" t="s">
         <v>29</v>
       </c>
       <c r="E127">
@@ -3118,16 +3127,16 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="1" t="s">
+      <c r="A128" t="s">
         <v>9</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="B128" t="s">
         <v>12</v>
       </c>
       <c r="C128">
         <v>1736.63</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="D128" t="s">
         <v>29</v>
       </c>
       <c r="E128">
@@ -3138,16 +3147,16 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="1" t="s">
+      <c r="A129" t="s">
         <v>11</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B129" t="s">
         <v>12</v>
       </c>
       <c r="C129">
         <v>2313.41</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="D129" t="s">
         <v>29</v>
       </c>
       <c r="E129">
@@ -3158,16 +3167,16 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="1" t="s">
+      <c r="A130" t="s">
         <v>11</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="B130" t="s">
         <v>12</v>
       </c>
       <c r="C130">
         <v>4846.2</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="D130" t="s">
         <v>29</v>
       </c>
       <c r="E130">
@@ -3178,16 +3187,16 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="1" t="s">
+      <c r="A131" t="s">
         <v>11</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="B131" t="s">
         <v>17</v>
       </c>
       <c r="C131">
         <v>1595.67</v>
       </c>
-      <c r="D131" s="1" t="s">
+      <c r="D131" t="s">
         <v>29</v>
       </c>
       <c r="E131">
@@ -3198,16 +3207,16 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="1" t="s">
+      <c r="A132" t="s">
         <v>11</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="B132" t="s">
         <v>17</v>
       </c>
       <c r="C132">
         <v>3815.93</v>
       </c>
-      <c r="D132" s="1" t="s">
+      <c r="D132" t="s">
         <v>29</v>
       </c>
       <c r="E132">
@@ -3218,16 +3227,16 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="1" t="s">
+      <c r="A133" t="s">
         <v>22</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="B133" t="s">
         <v>19</v>
       </c>
       <c r="C133">
         <v>3413.64</v>
       </c>
-      <c r="D133" s="1" t="s">
+      <c r="D133" t="s">
         <v>29</v>
       </c>
       <c r="E133">
@@ -3238,16 +3247,16 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="1" t="s">
+      <c r="A134" t="s">
         <v>11</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="B134" t="s">
         <v>12</v>
       </c>
       <c r="C134">
         <v>2691.78</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="D134" t="s">
         <v>29</v>
       </c>
       <c r="E134">
@@ -3258,16 +3267,16 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="1" t="s">
+      <c r="A135" t="s">
         <v>21</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="B135" t="s">
         <v>17</v>
       </c>
       <c r="C135">
         <v>4541.1400000000003</v>
       </c>
-      <c r="D135" s="1" t="s">
+      <c r="D135" t="s">
         <v>29</v>
       </c>
       <c r="E135">
@@ -3278,16 +3287,16 @@
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="1" t="s">
+      <c r="A136" t="s">
         <v>21</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="B136" t="s">
         <v>26</v>
       </c>
       <c r="C136">
         <v>3307.37</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="D136" t="s">
         <v>29</v>
       </c>
       <c r="E136">
@@ -3298,16 +3307,16 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="1" t="s">
+      <c r="A137" t="s">
         <v>23</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="B137" t="s">
         <v>26</v>
       </c>
       <c r="C137">
         <v>3503.97</v>
       </c>
-      <c r="D137" s="1" t="s">
+      <c r="D137" t="s">
         <v>29</v>
       </c>
       <c r="E137">
@@ -3318,16 +3327,16 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="1" t="s">
+      <c r="A138" t="s">
         <v>15</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="B138" t="s">
         <v>24</v>
       </c>
       <c r="C138">
         <v>1286.77</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="D138" t="s">
         <v>29</v>
       </c>
       <c r="E138">
@@ -3338,16 +3347,16 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="1" t="s">
+      <c r="A139" t="s">
         <v>6</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="B139" t="s">
         <v>24</v>
       </c>
       <c r="C139">
         <v>4079.52</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="D139" t="s">
         <v>29</v>
       </c>
       <c r="E139">
@@ -3358,16 +3367,16 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="1" t="s">
+      <c r="A140" t="s">
         <v>21</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="B140" t="s">
         <v>17</v>
       </c>
       <c r="C140">
         <v>3052.9</v>
       </c>
-      <c r="D140" s="1" t="s">
+      <c r="D140" t="s">
         <v>29</v>
       </c>
       <c r="E140">
@@ -3378,16 +3387,16 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="1" t="s">
+      <c r="A141" t="s">
         <v>11</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="B141" t="s">
         <v>17</v>
       </c>
       <c r="C141">
         <v>1555.89</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="D141" t="s">
         <v>29</v>
       </c>
       <c r="E141">
@@ -3398,16 +3407,16 @@
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="1" t="s">
+      <c r="A142" t="s">
         <v>21</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="B142" t="s">
         <v>12</v>
       </c>
       <c r="C142">
         <v>2293.98</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="D142" t="s">
         <v>29</v>
       </c>
       <c r="E142">
@@ -3418,16 +3427,16 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="1" t="s">
+      <c r="A143" t="s">
         <v>21</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="B143" t="s">
         <v>10</v>
       </c>
       <c r="C143">
         <v>3759.52</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="D143" t="s">
         <v>29</v>
       </c>
       <c r="E143">
@@ -3438,16 +3447,16 @@
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="1" t="s">
+      <c r="A144" t="s">
         <v>11</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="B144" t="s">
         <v>16</v>
       </c>
       <c r="C144">
         <v>1733.72</v>
       </c>
-      <c r="D144" s="1" t="s">
+      <c r="D144" t="s">
         <v>29</v>
       </c>
       <c r="E144">
@@ -3458,16 +3467,16 @@
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="1" t="s">
+      <c r="A145" t="s">
         <v>22</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="B145" t="s">
         <v>19</v>
       </c>
       <c r="C145">
         <v>4012.36</v>
       </c>
-      <c r="D145" s="1" t="s">
+      <c r="D145" t="s">
         <v>29</v>
       </c>
       <c r="E145">
@@ -3478,16 +3487,16 @@
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="1" t="s">
+      <c r="A146" t="s">
         <v>22</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="B146" t="s">
         <v>17</v>
       </c>
       <c r="C146">
         <v>980.95</v>
       </c>
-      <c r="D146" s="1" t="s">
+      <c r="D146" t="s">
         <v>29</v>
       </c>
       <c r="E146">
@@ -3498,16 +3507,16 @@
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="1" t="s">
+      <c r="A147" t="s">
         <v>21</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="B147" t="s">
         <v>26</v>
       </c>
       <c r="C147">
         <v>2929.81</v>
       </c>
-      <c r="D147" s="1" t="s">
+      <c r="D147" t="s">
         <v>29</v>
       </c>
       <c r="E147">
@@ -3518,16 +3527,16 @@
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="1" t="s">
+      <c r="A148" t="s">
         <v>9</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="B148" t="s">
         <v>7</v>
       </c>
       <c r="C148">
         <v>4289.1499999999996</v>
       </c>
-      <c r="D148" s="1" t="s">
+      <c r="D148" t="s">
         <v>29</v>
       </c>
       <c r="E148">
@@ -3538,16 +3547,16 @@
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="1" t="s">
+      <c r="A149" t="s">
         <v>18</v>
       </c>
-      <c r="B149" s="1" t="s">
+      <c r="B149" t="s">
         <v>17</v>
       </c>
       <c r="C149">
         <v>2844.31</v>
       </c>
-      <c r="D149" s="1" t="s">
+      <c r="D149" t="s">
         <v>29</v>
       </c>
       <c r="E149">
@@ -3558,16 +3567,16 @@
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A150" s="1" t="s">
+      <c r="A150" t="s">
         <v>11</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="B150" t="s">
         <v>12</v>
       </c>
       <c r="C150">
         <v>1551.7</v>
       </c>
-      <c r="D150" s="1" t="s">
+      <c r="D150" t="s">
         <v>29</v>
       </c>
       <c r="E150">
@@ -3578,16 +3587,16 @@
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A151" s="1" t="s">
+      <c r="A151" t="s">
         <v>15</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="B151" t="s">
         <v>16</v>
       </c>
       <c r="C151">
         <v>4019.13</v>
       </c>
-      <c r="D151" s="1" t="s">
+      <c r="D151" t="s">
         <v>29</v>
       </c>
       <c r="E151">
@@ -3598,16 +3607,16 @@
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A152" s="1" t="s">
+      <c r="A152" t="s">
         <v>13</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="B152" t="s">
         <v>7</v>
       </c>
       <c r="C152">
         <v>2446.2399999999998</v>
       </c>
-      <c r="D152" s="1" t="s">
+      <c r="D152" t="s">
         <v>29</v>
       </c>
       <c r="E152">
@@ -3618,16 +3627,16 @@
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A153" s="1" t="s">
+      <c r="A153" t="s">
         <v>18</v>
       </c>
-      <c r="B153" s="1" t="s">
+      <c r="B153" t="s">
         <v>7</v>
       </c>
       <c r="C153">
         <v>2992.11</v>
       </c>
-      <c r="D153" s="1" t="s">
+      <c r="D153" t="s">
         <v>29</v>
       </c>
       <c r="E153">
@@ -3638,16 +3647,16 @@
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A154" s="1" t="s">
+      <c r="A154" t="s">
         <v>13</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="B154" t="s">
         <v>7</v>
       </c>
       <c r="C154">
         <v>1874.86</v>
       </c>
-      <c r="D154" s="1" t="s">
+      <c r="D154" t="s">
         <v>29</v>
       </c>
       <c r="E154">
@@ -3658,16 +3667,16 @@
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A155" s="1" t="s">
+      <c r="A155" t="s">
         <v>11</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="B155" t="s">
         <v>16</v>
       </c>
       <c r="C155">
         <v>1903.17</v>
       </c>
-      <c r="D155" s="1" t="s">
+      <c r="D155" t="s">
         <v>29</v>
       </c>
       <c r="E155">
@@ -3678,16 +3687,16 @@
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A156" s="1" t="s">
+      <c r="A156" t="s">
         <v>11</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="B156" t="s">
         <v>17</v>
       </c>
       <c r="C156">
         <v>2820.56</v>
       </c>
-      <c r="D156" s="1" t="s">
+      <c r="D156" t="s">
         <v>29</v>
       </c>
       <c r="E156">
@@ -3698,16 +3707,16 @@
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A157" s="1" t="s">
+      <c r="A157" t="s">
         <v>18</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="B157" t="s">
         <v>17</v>
       </c>
       <c r="C157">
         <v>2736.34</v>
       </c>
-      <c r="D157" s="1" t="s">
+      <c r="D157" t="s">
         <v>29</v>
       </c>
       <c r="E157">
@@ -3718,16 +3727,16 @@
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A158" s="1" t="s">
+      <c r="A158" t="s">
         <v>11</v>
       </c>
-      <c r="B158" s="1" t="s">
+      <c r="B158" t="s">
         <v>17</v>
       </c>
       <c r="C158">
         <v>1900.88</v>
       </c>
-      <c r="D158" s="1" t="s">
+      <c r="D158" t="s">
         <v>29</v>
       </c>
       <c r="E158">
@@ -3738,16 +3747,16 @@
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A159" s="1" t="s">
+      <c r="A159" t="s">
         <v>22</v>
       </c>
-      <c r="B159" s="1" t="s">
+      <c r="B159" t="s">
         <v>17</v>
       </c>
       <c r="C159">
         <v>4331.41</v>
       </c>
-      <c r="D159" s="1" t="s">
+      <c r="D159" t="s">
         <v>29</v>
       </c>
       <c r="E159">
@@ -3758,16 +3767,16 @@
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A160" s="1" t="s">
+      <c r="A160" t="s">
         <v>11</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="B160" t="s">
         <v>17</v>
       </c>
       <c r="C160">
         <v>3349.18</v>
       </c>
-      <c r="D160" s="1" t="s">
+      <c r="D160" t="s">
         <v>29</v>
       </c>
       <c r="E160">
@@ -3778,16 +3787,16 @@
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A161" s="1" t="s">
+      <c r="A161" t="s">
         <v>6</v>
       </c>
-      <c r="B161" s="1" t="s">
+      <c r="B161" t="s">
         <v>26</v>
       </c>
       <c r="C161">
         <v>806.78</v>
       </c>
-      <c r="D161" s="1" t="s">
+      <c r="D161" t="s">
         <v>30</v>
       </c>
       <c r="E161">
@@ -3798,16 +3807,16 @@
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A162" s="1" t="s">
+      <c r="A162" t="s">
         <v>11</v>
       </c>
-      <c r="B162" s="1" t="s">
+      <c r="B162" t="s">
         <v>26</v>
       </c>
       <c r="C162">
         <v>4201.76</v>
       </c>
-      <c r="D162" s="1" t="s">
+      <c r="D162" t="s">
         <v>30</v>
       </c>
       <c r="E162">
@@ -3818,16 +3827,16 @@
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A163" s="1" t="s">
+      <c r="A163" t="s">
         <v>25</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="B163" t="s">
         <v>19</v>
       </c>
       <c r="C163">
         <v>885.46</v>
       </c>
-      <c r="D163" s="1" t="s">
+      <c r="D163" t="s">
         <v>30</v>
       </c>
       <c r="E163">
@@ -3838,16 +3847,16 @@
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A164" s="1" t="s">
+      <c r="A164" t="s">
         <v>22</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="B164" t="s">
         <v>19</v>
       </c>
       <c r="C164">
         <v>4523.8599999999997</v>
       </c>
-      <c r="D164" s="1" t="s">
+      <c r="D164" t="s">
         <v>30</v>
       </c>
       <c r="E164">
@@ -3858,16 +3867,16 @@
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A165" s="1" t="s">
+      <c r="A165" t="s">
         <v>25</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="B165" t="s">
         <v>19</v>
       </c>
       <c r="C165">
         <v>1363.4</v>
       </c>
-      <c r="D165" s="1" t="s">
+      <c r="D165" t="s">
         <v>30</v>
       </c>
       <c r="E165">
@@ -3878,16 +3887,16 @@
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A166" s="1" t="s">
+      <c r="A166" t="s">
         <v>23</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="B166" t="s">
         <v>12</v>
       </c>
       <c r="C166">
         <v>1955.17</v>
       </c>
-      <c r="D166" s="1" t="s">
+      <c r="D166" t="s">
         <v>30</v>
       </c>
       <c r="E166">
@@ -3898,16 +3907,16 @@
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A167" s="1" t="s">
+      <c r="A167" t="s">
         <v>18</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="B167" t="s">
         <v>20</v>
       </c>
       <c r="C167">
         <v>1519.95</v>
       </c>
-      <c r="D167" s="1" t="s">
+      <c r="D167" t="s">
         <v>30</v>
       </c>
       <c r="E167">
@@ -3918,16 +3927,16 @@
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A168" s="1" t="s">
+      <c r="A168" t="s">
         <v>23</v>
       </c>
-      <c r="B168" s="1" t="s">
+      <c r="B168" t="s">
         <v>24</v>
       </c>
       <c r="C168">
         <v>2097.48</v>
       </c>
-      <c r="D168" s="1" t="s">
+      <c r="D168" t="s">
         <v>30</v>
       </c>
       <c r="E168">
@@ -3938,16 +3947,16 @@
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A169" s="1" t="s">
+      <c r="A169" t="s">
         <v>22</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="B169" t="s">
         <v>24</v>
       </c>
       <c r="C169">
         <v>812.41</v>
       </c>
-      <c r="D169" s="1" t="s">
+      <c r="D169" t="s">
         <v>30</v>
       </c>
       <c r="E169">
@@ -3958,16 +3967,16 @@
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A170" s="1" t="s">
+      <c r="A170" t="s">
         <v>11</v>
       </c>
-      <c r="B170" s="1" t="s">
+      <c r="B170" t="s">
         <v>17</v>
       </c>
       <c r="C170">
         <v>1108.25</v>
       </c>
-      <c r="D170" s="1" t="s">
+      <c r="D170" t="s">
         <v>30</v>
       </c>
       <c r="E170">
@@ -3978,16 +3987,16 @@
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A171" s="1" t="s">
+      <c r="A171" t="s">
         <v>18</v>
       </c>
-      <c r="B171" s="1" t="s">
+      <c r="B171" t="s">
         <v>20</v>
       </c>
       <c r="C171">
         <v>2972.88</v>
       </c>
-      <c r="D171" s="1" t="s">
+      <c r="D171" t="s">
         <v>30</v>
       </c>
       <c r="E171">
@@ -3998,16 +4007,16 @@
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A172" s="1" t="s">
+      <c r="A172" t="s">
         <v>18</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="B172" t="s">
         <v>20</v>
       </c>
       <c r="C172">
         <v>1998.51</v>
       </c>
-      <c r="D172" s="1" t="s">
+      <c r="D172" t="s">
         <v>30</v>
       </c>
       <c r="E172">
@@ -4018,16 +4027,16 @@
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A173" s="1" t="s">
+      <c r="A173" t="s">
         <v>13</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="B173" t="s">
         <v>14</v>
       </c>
       <c r="C173">
         <v>4973.63</v>
       </c>
-      <c r="D173" s="1" t="s">
+      <c r="D173" t="s">
         <v>30</v>
       </c>
       <c r="E173">
@@ -4038,16 +4047,16 @@
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A174" s="1" t="s">
+      <c r="A174" t="s">
         <v>23</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="B174" t="s">
         <v>12</v>
       </c>
       <c r="C174">
         <v>3207.25</v>
       </c>
-      <c r="D174" s="1" t="s">
+      <c r="D174" t="s">
         <v>30</v>
       </c>
       <c r="E174">
@@ -4058,16 +4067,16 @@
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A175" s="1" t="s">
+      <c r="A175" t="s">
         <v>11</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="B175" t="s">
         <v>26</v>
       </c>
       <c r="C175">
         <v>4809.3100000000004</v>
       </c>
-      <c r="D175" s="1" t="s">
+      <c r="D175" t="s">
         <v>30</v>
       </c>
       <c r="E175">
@@ -4078,16 +4087,16 @@
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A176" s="1" t="s">
+      <c r="A176" t="s">
         <v>21</v>
       </c>
-      <c r="B176" s="1" t="s">
+      <c r="B176" t="s">
         <v>17</v>
       </c>
       <c r="C176">
         <v>1288.8599999999999</v>
       </c>
-      <c r="D176" s="1" t="s">
+      <c r="D176" t="s">
         <v>30</v>
       </c>
       <c r="E176">
@@ -4098,16 +4107,16 @@
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A177" s="1" t="s">
+      <c r="A177" t="s">
         <v>23</v>
       </c>
-      <c r="B177" s="1" t="s">
+      <c r="B177" t="s">
         <v>26</v>
       </c>
       <c r="C177">
         <v>935.04</v>
       </c>
-      <c r="D177" s="1" t="s">
+      <c r="D177" t="s">
         <v>30</v>
       </c>
       <c r="E177">
@@ -4118,16 +4127,16 @@
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A178" s="1" t="s">
+      <c r="A178" t="s">
         <v>15</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="B178" t="s">
         <v>16</v>
       </c>
       <c r="C178">
         <v>3902.73</v>
       </c>
-      <c r="D178" s="1" t="s">
+      <c r="D178" t="s">
         <v>30</v>
       </c>
       <c r="E178">
@@ -4138,16 +4147,16 @@
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A179" s="1" t="s">
+      <c r="A179" t="s">
         <v>22</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="B179" t="s">
         <v>17</v>
       </c>
       <c r="C179">
         <v>4833.17</v>
       </c>
-      <c r="D179" s="1" t="s">
+      <c r="D179" t="s">
         <v>30</v>
       </c>
       <c r="E179">
@@ -4158,16 +4167,16 @@
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A180" s="1" t="s">
+      <c r="A180" t="s">
         <v>9</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="B180" t="s">
         <v>26</v>
       </c>
       <c r="C180">
         <v>1185.8699999999999</v>
       </c>
-      <c r="D180" s="1" t="s">
+      <c r="D180" t="s">
         <v>30</v>
       </c>
       <c r="E180">
@@ -4178,16 +4187,16 @@
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A181" s="1" t="s">
+      <c r="A181" t="s">
         <v>13</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="B181" t="s">
         <v>7</v>
       </c>
       <c r="C181">
         <v>3898.72</v>
       </c>
-      <c r="D181" s="1" t="s">
+      <c r="D181" t="s">
         <v>30</v>
       </c>
       <c r="E181">
@@ -4198,16 +4207,16 @@
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A182" s="1" t="s">
+      <c r="A182" t="s">
         <v>11</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="B182" t="s">
         <v>26</v>
       </c>
       <c r="C182">
         <v>1074.71</v>
       </c>
-      <c r="D182" s="1" t="s">
+      <c r="D182" t="s">
         <v>30</v>
       </c>
       <c r="E182">
@@ -4218,16 +4227,16 @@
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A183" s="1" t="s">
+      <c r="A183" t="s">
         <v>11</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="B183" t="s">
         <v>17</v>
       </c>
       <c r="C183">
         <v>1048.49</v>
       </c>
-      <c r="D183" s="1" t="s">
+      <c r="D183" t="s">
         <v>30</v>
       </c>
       <c r="E183">
@@ -4238,16 +4247,16 @@
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A184" s="1" t="s">
+      <c r="A184" t="s">
         <v>23</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="B184" t="s">
         <v>24</v>
       </c>
       <c r="C184">
         <v>2120.61</v>
       </c>
-      <c r="D184" s="1" t="s">
+      <c r="D184" t="s">
         <v>30</v>
       </c>
       <c r="E184">
@@ -4258,16 +4267,16 @@
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A185" s="1" t="s">
+      <c r="A185" t="s">
         <v>15</v>
       </c>
-      <c r="B185" s="1" t="s">
+      <c r="B185" t="s">
         <v>16</v>
       </c>
       <c r="C185">
         <v>4637.26</v>
       </c>
-      <c r="D185" s="1" t="s">
+      <c r="D185" t="s">
         <v>30</v>
       </c>
       <c r="E185">
@@ -4278,16 +4287,16 @@
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A186" s="1" t="s">
+      <c r="A186" t="s">
         <v>23</v>
       </c>
-      <c r="B186" s="1" t="s">
+      <c r="B186" t="s">
         <v>26</v>
       </c>
       <c r="C186">
         <v>2926.23</v>
       </c>
-      <c r="D186" s="1" t="s">
+      <c r="D186" t="s">
         <v>30</v>
       </c>
       <c r="E186">
@@ -4298,16 +4307,16 @@
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A187" s="1" t="s">
+      <c r="A187" t="s">
         <v>11</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="B187" t="s">
         <v>12</v>
       </c>
       <c r="C187">
         <v>1882.8</v>
       </c>
-      <c r="D187" s="1" t="s">
+      <c r="D187" t="s">
         <v>30</v>
       </c>
       <c r="E187">
@@ -4318,16 +4327,16 @@
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A188" s="1" t="s">
+      <c r="A188" t="s">
         <v>21</v>
       </c>
-      <c r="B188" s="1" t="s">
+      <c r="B188" t="s">
         <v>17</v>
       </c>
       <c r="C188">
         <v>4450.88</v>
       </c>
-      <c r="D188" s="1" t="s">
+      <c r="D188" t="s">
         <v>30</v>
       </c>
       <c r="E188">
@@ -4338,16 +4347,16 @@
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A189" s="1" t="s">
+      <c r="A189" t="s">
         <v>6</v>
       </c>
-      <c r="B189" s="1" t="s">
+      <c r="B189" t="s">
         <v>24</v>
       </c>
       <c r="C189">
         <v>864.14</v>
       </c>
-      <c r="D189" s="1" t="s">
+      <c r="D189" t="s">
         <v>30</v>
       </c>
       <c r="E189">
@@ -4358,16 +4367,16 @@
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A190" s="1" t="s">
+      <c r="A190" t="s">
         <v>6</v>
       </c>
-      <c r="B190" s="1" t="s">
+      <c r="B190" t="s">
         <v>14</v>
       </c>
       <c r="C190">
         <v>1280.8599999999999</v>
       </c>
-      <c r="D190" s="1" t="s">
+      <c r="D190" t="s">
         <v>30</v>
       </c>
       <c r="E190">
@@ -4378,16 +4387,16 @@
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A191" s="1" t="s">
+      <c r="A191" t="s">
         <v>15</v>
       </c>
-      <c r="B191" s="1" t="s">
+      <c r="B191" t="s">
         <v>17</v>
       </c>
       <c r="C191">
         <v>2057.4499999999998</v>
       </c>
-      <c r="D191" s="1" t="s">
+      <c r="D191" t="s">
         <v>30</v>
       </c>
       <c r="E191">
@@ -4398,16 +4407,16 @@
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A192" s="1" t="s">
+      <c r="A192" t="s">
         <v>21</v>
       </c>
-      <c r="B192" s="1" t="s">
+      <c r="B192" t="s">
         <v>26</v>
       </c>
       <c r="C192">
         <v>4890.25</v>
       </c>
-      <c r="D192" s="1" t="s">
+      <c r="D192" t="s">
         <v>30</v>
       </c>
       <c r="E192">
@@ -4418,16 +4427,16 @@
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A193" s="1" t="s">
+      <c r="A193" t="s">
         <v>15</v>
       </c>
-      <c r="B193" s="1" t="s">
+      <c r="B193" t="s">
         <v>16</v>
       </c>
       <c r="C193">
         <v>4201.16</v>
       </c>
-      <c r="D193" s="1" t="s">
+      <c r="D193" t="s">
         <v>30</v>
       </c>
       <c r="E193">
@@ -4438,16 +4447,16 @@
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A194" s="1" t="s">
+      <c r="A194" t="s">
         <v>15</v>
       </c>
-      <c r="B194" s="1" t="s">
+      <c r="B194" t="s">
         <v>16</v>
       </c>
       <c r="C194">
         <v>3139.74</v>
       </c>
-      <c r="D194" s="1" t="s">
+      <c r="D194" t="s">
         <v>30</v>
       </c>
       <c r="E194">
@@ -4458,16 +4467,16 @@
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A195" s="1" t="s">
+      <c r="A195" t="s">
         <v>21</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="B195" t="s">
         <v>10</v>
       </c>
       <c r="C195">
         <v>4652.41</v>
       </c>
-      <c r="D195" s="1" t="s">
+      <c r="D195" t="s">
         <v>30</v>
       </c>
       <c r="E195">
@@ -4478,16 +4487,16 @@
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A196" s="1" t="s">
+      <c r="A196" t="s">
         <v>13</v>
       </c>
-      <c r="B196" s="1" t="s">
+      <c r="B196" t="s">
         <v>14</v>
       </c>
       <c r="C196">
         <v>2532.9499999999998</v>
       </c>
-      <c r="D196" s="1" t="s">
+      <c r="D196" t="s">
         <v>30</v>
       </c>
       <c r="E196">
@@ -4498,16 +4507,16 @@
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A197" s="1" t="s">
+      <c r="A197" t="s">
         <v>15</v>
       </c>
-      <c r="B197" s="1" t="s">
+      <c r="B197" t="s">
         <v>24</v>
       </c>
       <c r="C197">
         <v>3628.15</v>
       </c>
-      <c r="D197" s="1" t="s">
+      <c r="D197" t="s">
         <v>30</v>
       </c>
       <c r="E197">
@@ -4518,16 +4527,16 @@
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A198" s="1" t="s">
+      <c r="A198" t="s">
         <v>15</v>
       </c>
-      <c r="B198" s="1" t="s">
+      <c r="B198" t="s">
         <v>16</v>
       </c>
       <c r="C198">
         <v>2319.4299999999998</v>
       </c>
-      <c r="D198" s="1" t="s">
+      <c r="D198" t="s">
         <v>30</v>
       </c>
       <c r="E198">
@@ -4538,16 +4547,16 @@
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A199" s="1" t="s">
+      <c r="A199" t="s">
         <v>9</v>
       </c>
-      <c r="B199" s="1" t="s">
+      <c r="B199" t="s">
         <v>20</v>
       </c>
       <c r="C199">
         <v>2761.55</v>
       </c>
-      <c r="D199" s="1" t="s">
+      <c r="D199" t="s">
         <v>30</v>
       </c>
       <c r="E199">
@@ -4558,16 +4567,16 @@
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A200" s="1" t="s">
+      <c r="A200" t="s">
         <v>9</v>
       </c>
-      <c r="B200" s="1" t="s">
+      <c r="B200" t="s">
         <v>12</v>
       </c>
       <c r="C200">
         <v>3615.96</v>
       </c>
-      <c r="D200" s="1" t="s">
+      <c r="D200" t="s">
         <v>30</v>
       </c>
       <c r="E200">
@@ -4578,16 +4587,16 @@
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A201" s="1" t="s">
+      <c r="A201" t="s">
         <v>23</v>
       </c>
-      <c r="B201" s="1" t="s">
+      <c r="B201" t="s">
         <v>24</v>
       </c>
       <c r="C201">
         <v>3288.15</v>
       </c>
-      <c r="D201" s="1" t="s">
+      <c r="D201" t="s">
         <v>30</v>
       </c>
       <c r="E201">
